--- a/artfynd/A 19872-2025 artfynd.xlsx
+++ b/artfynd/A 19872-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076686</v>
       </c>
       <c r="B2" t="n">
-        <v>77934</v>
+        <v>77994</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076678</v>
       </c>
       <c r="B3" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076673</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19872-2025 artfynd.xlsx
+++ b/artfynd/A 19872-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076686</v>
       </c>
       <c r="B2" t="n">
-        <v>77994</v>
+        <v>77997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076678</v>
       </c>
       <c r="B3" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076673</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19872-2025 artfynd.xlsx
+++ b/artfynd/A 19872-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076686</v>
       </c>
       <c r="B2" t="n">
-        <v>77997</v>
+        <v>78001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076678</v>
       </c>
       <c r="B3" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076673</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19872-2025 artfynd.xlsx
+++ b/artfynd/A 19872-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076686</v>
       </c>
       <c r="B2" t="n">
-        <v>78001</v>
+        <v>78003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076678</v>
       </c>
       <c r="B3" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076673</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19872-2025 artfynd.xlsx
+++ b/artfynd/A 19872-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076686</v>
       </c>
       <c r="B2" t="n">
-        <v>78003</v>
+        <v>78006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076678</v>
       </c>
       <c r="B3" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076673</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
